--- a/deliverables/夏春长三角合作方案_配套测算与清单.xlsx
+++ b/deliverables/夏春长三角合作方案_配套测算与清单.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分工分润" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务测算" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待办" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI与转正门槛" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI与转长期" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,7 +681,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心 × 杨浦区科技企业联合会   |   2026年7月   |  与 PPT 方案配套使用</t>
+          <t>复旦大学住房政策研究中心 × 上海市杨浦区科技企业联合会 × 上海市科技企业联合会   |   2026年7月   |  与 PPT 方案配套使用</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>长期战略协作 + 先行约 3 个月的敏感性适配过渡期（达标转正）。</t>
+          <t>长期深化合作 + 先行约 3 个月的适度过渡期（双方适应与适配）；过渡顺畅、无重大问题即自动转为长期。</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心；杨浦区科技企业联合会。</t>
+          <t>复旦大学住房政策研究中心；上海市杨浦区科技企业联合会（为主）；上海市科技企业联合会。三家联同开展服务。</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>以夏春公开访谈 / 公众号 · 视频号观点与双方沟通纪要为依据（见“语录解析”）。</t>
+          <t>以夏春公开访谈 / 公众号 · 视频号观点与双方前期沟通为依据（见“语录解析”）。</t>
         </is>
       </c>
     </row>
@@ -837,19 +837,19 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>源自沟通纪要“待解决问题”的风险项、应对措施、责任方与优先级。</t>
+          <t>双方前期沟通中的待解决问题、应对措施、责任方与优先级。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>⑧ KPI与转正门槛</t>
+          <t>⑧ KPI与转长期安排</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>过渡期与长期的关键指标及由过渡转长期独家的达标条件。</t>
+          <t>过渡期与长期的关键参考指标，及过渡顺畅即自动转长期的安排。</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>摘自公开访谈 / 公众号 · 视频号 + 双方沟通纪要，提炼为长三角合作切入点</t>
+          <t>摘自公开访谈 / 公众号 · 视频号 + 双方前期沟通，提炼为长三角合作切入点</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>直接呼应纪要中的香港游学 RWA、中东资金窗口期。</t>
+          <t>直接呼应双方共同关注的香港游学 RWA、中东资金窗口期。</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>（纪要）香港游学需夏春博士全程参与；方案由夏春主导决策。</t>
+          <t>（前期沟通）香港游学需夏春先生全程参与；方案由夏春先生主导决策。</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>沟通纪要</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>（纪要）依托复旦 / 科委背书突破企业制度限制，落地头部科技企业参访。</t>
+          <t>（前期沟通）依托复旦 / 科技企业联合会背书突破企业制度限制，落地头部科技企业参访。</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>沟通纪要</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>我方双背书正是突破点，与纪要重点高度契合。</t>
+          <t>我方多方背书正是突破点，与双方前期沟通重点高度契合。</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>以复旦 + 杨浦科委背书，落地 AI / 科技前沿头部企业参访。</t>
+          <t>以复旦 + 市 / 区科技企业联合会背书，落地 AI / 科技前沿头部企业参访。</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3 个月过渡期行动计划（敏感性适配 → 达标转正）</t>
+          <t>3 个月适度过渡期行动计划（双方适应与适配）</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>对齐目标与边界，确认过渡期授权范围</t>
+          <t>对齐目标与边界，确认过渡期独家授权范围</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>起草并会签合作备忘录（MOU）与区域授权草案</t>
+          <t>起草并会签合作备忘录（MOU）与区域独家授权草案</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>客户 / 会员画像盘点，明确客户归属与分润规则</t>
+          <t>客户 / 会员画像盘点，明确客户归属与收益分配规则</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1603,7 +1603,7 @@
       <c r="A12" s="20" t="inlineStr">
         <is>
           <t>第3月
-复盘转正</t>
+复盘转长期</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -1641,7 +1641,7 @@
       <c r="A13" s="20" t="inlineStr">
         <is>
           <t>第3月
-复盘转正</t>
+复盘转长期</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       <c r="A14" s="20" t="inlineStr">
         <is>
           <t>第3月
-复盘转正</t>
+复盘转长期</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>财务复盘、客户满意度与数据分析</t>
+          <t>运作复盘、双方磨合与客户满意度分析</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1713,7 +1713,7 @@
       <c r="A15" s="20" t="inlineStr">
         <is>
           <t>第3月
-复盘转正</t>
+复盘转长期</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>对照 KPI 评估，签署长期区域独家总代理协议</t>
+          <t>过渡顺畅、无重大问题，自动转长期并会签区域独家总代理协议</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>★ 转正</t>
+          <t>★ 转长期</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>结合夏春观点与沟通纪要；客单价 / 毛利为区间预估，需按实际招商调整</t>
+          <t>结合夏春观点与双方前期沟通；客单价 / 毛利为区间预估，需按实际招商调整</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>杨浦科委 + 复旦背书</t>
+          <t>市 / 区科技企业联合会 + 复旦背书</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>只做长三角区域增量，边界清晰、互补不重叠（呼应纪要“主导权 / 客户归属”）</t>
+          <t>只做长三角区域增量，边界清晰、互补不重叠（明确主导权 / 客户归属）</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>复旦 + 杨浦科委 双背书 + 本地网络</t>
+          <t>复旦 + 市 / 区科技企业联合会 背书 + 本地网络</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>多数源自双方沟通纪要“待解决问题 / 待办事项”，过渡期内逐项落定并写入 MOU</t>
+          <t>多为双方前期沟通中的待解决问题 / 待办事项，过渡期内逐项落定并写入 MOU</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>纪要·待解决</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>纪要·待解决</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>纪要·待解决</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>纪要·待解决</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>提供参访 / 分润 / 深圳方案案例</t>
+          <t>参访 / 分配 / 落地案例参考</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>纪要·待办(胡)</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>沟通中由对方团队提供既有案例参考，我方据此做长三角适配。</t>
+          <t>参考既有成熟活动案例，我方据此做长三角本地化适配与收益分配设计。</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>对方团队</t>
+          <t>我方</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>纪要·待办</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>纪要·待办</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>纪要·待办</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>过渡期第 1 月内会签 MOU 与区域授权草案。</t>
+          <t>过渡期第 1 月内会签 MOU 与区域独家授权草案。</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>纪要·待办</t>
+          <t>前期沟通</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -3405,14 +3405,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KPI 与由过渡转长期独家的门槛</t>
+          <t>KPI 与转长期安排</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>过渡期达标即触发长期区域独家总代理；目标为建议值，签约前双方确认</t>
+          <t>过渡顺畅即自动转为长期区域独家总代理；下列为过渡期与长期的参考指标（非硬性考核门槛），签约前双方确认</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>过渡期目标（约3个月）</t>
+          <t>过渡期参考值（约3个月）</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -3621,7 +3621,7 @@
     <row r="12">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>转正门槛：过渡期同时满足“活动场次 ≥ 3、营收 ≥ 60 万、毛利率 ≥ 60%、满意度 ≥ 4.5”，即由过渡期自动转为长期区域独家总代理并会签正式协议。</t>
+          <t>转长期安排：三个月适度过渡期为双方适应与适配阶段；若运作顺畅、无重大问题，即自动转为长期区域独家总代理并会签正式协议。上列指标仅作过渡期健康度参考，非硬性考核门槛。</t>
         </is>
       </c>
       <c r="B12" s="41" t="n"/>
